--- a/data/system_data.xlsx
+++ b/data/system_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\0327_ecatalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AF6746-57B3-4951-8EAD-505C628A0236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB018CB-CB98-4090-BE31-2A730C6E141E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{20599BEF-A927-4261-B7A2-D48F6DBDC390}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" firstSheet="1" activeTab="2" xr2:uid="{20599BEF-A927-4261-B7A2-D48F6DBDC390}"/>
   </bookViews>
   <sheets>
     <sheet name="Pneumatic Cylinder" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="165">
   <si>
     <t>Q-Code</t>
   </si>
@@ -532,6 +532,30 @@
   <si>
     <t>https://woonyoung.com/page/s0201_mid.php?gcatecode=1337921322&amp;gcname=%EC%A7%80%EB%9D%BD%EA%B2%80%EC%B6%9C%EA%B3%84%EC%A0%84%EA%B8%B0&amp;gn_sub=GFR</t>
   </si>
+  <si>
+    <t>HANA MECHANICAL&amp;ELECTRICAL</t>
+  </si>
+  <si>
+    <t>SEW</t>
+  </si>
+  <si>
+    <t>HYOSUNG</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>SAMWHADSP</t>
+  </si>
+  <si>
+    <t>SAM WHA DSP</t>
+  </si>
+  <si>
+    <t>KYONGBO</t>
+  </si>
 </sst>
 </file>
 
@@ -770,11 +794,11 @@
       <sheetName val="protection Relay 상세사양"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>ITEM코드</v>
@@ -12125,8 +12149,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>ITEM코드</v>
@@ -17336,10 +17360,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>ITEM코드</v>
@@ -25190,9 +25214,8 @@
         <f>VLOOKUP(A2,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>DHHM8-9175-43</v>
       </c>
-      <c r="E2" t="str">
-        <f>VLOOKUP(A2,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HANA MECHANICAL&amp;ELECTRICAL</v>
+      <c r="E2" t="s">
+        <v>157</v>
       </c>
       <c r="F2" t="str">
         <f>VLOOKUP(A2,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25245,9 +25268,8 @@
         <f>VLOOKUP(A3,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>R47 DRN100L4</v>
       </c>
-      <c r="E3" t="str">
-        <f>VLOOKUP(A3,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>SEW</v>
+      <c r="E3" t="s">
+        <v>158</v>
       </c>
       <c r="F3" t="str">
         <f>VLOOKUP(A3,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25302,9 +25324,8 @@
         <f>VLOOKUP(A4,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>RPH</v>
       </c>
-      <c r="E4" t="str">
-        <f>VLOOKUP(A4,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E4" t="s">
+        <v>159</v>
       </c>
       <c r="F4" t="str">
         <f>VLOOKUP(A4,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25359,9 +25380,8 @@
         <f>VLOOKUP(A5,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>RPH</v>
       </c>
-      <c r="E5" t="str">
-        <f>VLOOKUP(A5,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E5" t="s">
+        <v>159</v>
       </c>
       <c r="F5" t="str">
         <f>VLOOKUP(A5,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25416,9 +25436,8 @@
         <f>VLOOKUP(A6,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>HLA020101057587</v>
       </c>
-      <c r="E6" t="str">
-        <f>VLOOKUP(A6,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E6" t="s">
+        <v>159</v>
       </c>
       <c r="F6" t="str">
         <f>VLOOKUP(A6,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25471,9 +25490,8 @@
         <f>VLOOKUP(A7,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>HMA01080000560</v>
       </c>
-      <c r="E7" t="str">
-        <f>VLOOKUP(A7,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E7" t="s">
+        <v>159</v>
       </c>
       <c r="F7" t="str">
         <f>VLOOKUP(A7,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25526,9 +25544,8 @@
         <f>VLOOKUP(A8,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>HLA020101057590</v>
       </c>
-      <c r="E8" t="str">
-        <f>VLOOKUP(A8,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E8" t="s">
+        <v>159</v>
       </c>
       <c r="F8" t="str">
         <f>VLOOKUP(A8,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25581,9 +25598,8 @@
         <f>VLOOKUP(A9,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>HLA020101057591</v>
       </c>
-      <c r="E9" t="str">
-        <f>VLOOKUP(A9,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E9" t="s">
+        <v>159</v>
       </c>
       <c r="F9" t="str">
         <f>VLOOKUP(A9,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25636,9 +25652,8 @@
         <f>VLOOKUP(A10,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>HLA020101057588</v>
       </c>
-      <c r="E10" t="str">
-        <f>VLOOKUP(A10,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E10" t="s">
+        <v>159</v>
       </c>
       <c r="F10" t="str">
         <f>VLOOKUP(A10,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25691,9 +25706,8 @@
         <f>VLOOKUP(A11,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>HMA01080000560</v>
       </c>
-      <c r="E11" t="str">
-        <f>VLOOKUP(A11,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>HYOSUNG</v>
+      <c r="E11" t="s">
+        <v>159</v>
       </c>
       <c r="F11" t="str">
         <f>VLOOKUP(A11,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -25746,9 +25760,8 @@
         <f>VLOOKUP(A12,'[1]모터 상세사양값'!$A$1:$CG$27,28,0)</f>
         <v>JK-BT2200</v>
       </c>
-      <c r="E12" t="str">
-        <f>VLOOKUP(A12,'[1]모터 상세사양값'!$A$1:$CG$27,30,0)</f>
-        <v>JEIL REDUCER</v>
+      <c r="E12" t="s">
+        <v>77</v>
       </c>
       <c r="F12" t="str">
         <f>VLOOKUP(A12,'[1]모터 상세사양값'!$A$1:$CG$27,52,0)</f>
@@ -26123,9 +26136,8 @@
         <f>VLOOKUP(A2,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DMP06I-T</v>
       </c>
-      <c r="E2" t="str">
-        <f>VLOOKUP(A2,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>LS</v>
+      <c r="E2" t="s">
+        <v>160</v>
       </c>
       <c r="F2" t="str">
         <f>VLOOKUP(A2,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26164,9 +26176,8 @@
         <f>VLOOKUP(A3,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DMP65I-TZ</v>
       </c>
-      <c r="E3" t="str">
-        <f>VLOOKUP(A3,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>LS</v>
+      <c r="E3" t="s">
+        <v>160</v>
       </c>
       <c r="F3" t="str">
         <f>VLOOKUP(A3,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26205,9 +26216,8 @@
         <f>VLOOKUP(A4,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DMP65I-T</v>
       </c>
-      <c r="E4" t="str">
-        <f>VLOOKUP(A4,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>LS</v>
+      <c r="E4" t="s">
+        <v>160</v>
       </c>
       <c r="F4" t="str">
         <f>VLOOKUP(A4,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26246,9 +26256,8 @@
         <f>VLOOKUP(A5,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>WYGF-D12NC</v>
       </c>
-      <c r="E5" t="str">
-        <f>VLOOKUP(A5,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>WOONYOUNG</v>
+      <c r="E5" t="s">
+        <v>113</v>
       </c>
       <c r="F5" t="str">
         <f>VLOOKUP(A5,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26287,9 +26296,8 @@
         <f>VLOOKUP(A6,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>3RU2146-4KB0</v>
       </c>
-      <c r="E6" t="str">
-        <f>VLOOKUP(A6,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SIEMENS</v>
+      <c r="E6" t="s">
+        <v>161</v>
       </c>
       <c r="F6" t="str">
         <f>VLOOKUP(A6,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26328,9 +26336,8 @@
         <f>VLOOKUP(A7,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>3RU5146-4KB0</v>
       </c>
-      <c r="E7" t="str">
-        <f>VLOOKUP(A7,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SIEMENS</v>
+      <c r="E7" t="s">
+        <v>161</v>
       </c>
       <c r="F7" t="str">
         <f>VLOOKUP(A7,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26369,9 +26376,8 @@
         <f>VLOOKUP(A8,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DSP-AOM-02Z7-ZCT-F</v>
       </c>
-      <c r="E8" t="str">
-        <f>VLOOKUP(A8,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SAMWHADSP</v>
+      <c r="E8" t="s">
+        <v>162</v>
       </c>
       <c r="F8" t="str">
         <f>VLOOKUP(A8,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26410,9 +26416,8 @@
         <f>VLOOKUP(A9,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DSP-AOM-10Z7-ZCT-F</v>
       </c>
-      <c r="E9" t="str">
-        <f>VLOOKUP(A9,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SAMWHADSP</v>
+      <c r="E9" t="s">
+        <v>162</v>
       </c>
       <c r="F9" t="str">
         <f>VLOOKUP(A9,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26451,9 +26456,8 @@
         <f>VLOOKUP(A10,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DSP-AOM-70Z7-ZCT-F</v>
       </c>
-      <c r="E10" t="str">
-        <f>VLOOKUP(A10,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SAMWHADSP</v>
+      <c r="E10" t="s">
+        <v>162</v>
       </c>
       <c r="F10" t="str">
         <f>VLOOKUP(A10,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26492,9 +26496,8 @@
         <f>VLOOKUP(A11,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DSP-AOL-02Z7-F</v>
       </c>
-      <c r="E11" t="str">
-        <f>VLOOKUP(A11,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SAMWHADSP</v>
+      <c r="E11" t="s">
+        <v>162</v>
       </c>
       <c r="F11" t="str">
         <f>VLOOKUP(A11,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26533,9 +26536,8 @@
         <f>VLOOKUP(A12,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DSP-IR-Z7-C-F</v>
       </c>
-      <c r="E12" t="str">
-        <f>VLOOKUP(A12,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SAM WHA DSP</v>
+      <c r="E12" t="s">
+        <v>163</v>
       </c>
       <c r="F12" t="str">
         <f>VLOOKUP(A12,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26574,9 +26576,8 @@
         <f>VLOOKUP(A13,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>DSP-IRM-Z7-C-F</v>
       </c>
-      <c r="E13" t="str">
-        <f>VLOOKUP(A13,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>SAM WHA DSP</v>
+      <c r="E13" t="s">
+        <v>163</v>
       </c>
       <c r="F13" t="str">
         <f>VLOOKUP(A13,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26615,9 +26616,8 @@
         <f>VLOOKUP(A14,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>WYER-D16NC</v>
       </c>
-      <c r="E14" t="str">
-        <f>VLOOKUP(A14,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>WOONYOUNG</v>
+      <c r="E14" t="s">
+        <v>113</v>
       </c>
       <c r="F14" t="str">
         <f>VLOOKUP(A14,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26656,9 +26656,8 @@
         <f>VLOOKUP(A15,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>WYGF-D11T</v>
       </c>
-      <c r="E15" t="str">
-        <f>VLOOKUP(A15,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>WOONYOUNG</v>
+      <c r="E15" t="s">
+        <v>113</v>
       </c>
       <c r="F15" t="str">
         <f>VLOOKUP(A15,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
@@ -26697,9 +26696,8 @@
         <f>VLOOKUP(A16,'[1]protection Relay 상세사양'!$A$1:$CG$47,32,0)</f>
         <v>GD12-L05A</v>
       </c>
-      <c r="E16" t="str">
-        <f>VLOOKUP(A16,'[1]protection Relay 상세사양'!$A$1:$CG$47,34,0)</f>
-        <v>KYONGBO</v>
+      <c r="E16" t="s">
+        <v>164</v>
       </c>
       <c r="F16" t="str">
         <f>VLOOKUP(A16,'[1]protection Relay 상세사양'!$A$1:$CG$47,50,0)</f>
